--- a/RawMaterial_Elastic_Template.xlsx
+++ b/RawMaterial_Elastic_Template.xlsx
@@ -886,9 +886,12 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"warp,weft,covering,Rubber,other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Suppliers!$A$2:$A$1000</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1165,6 +1168,17 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=RawMaterials!$A$2:$A$1000</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=RawMaterials!$A$2:$A$1000</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=RawMaterials!$A$2:$A$1000</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1282,6 +1296,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=RawMaterials!$A$2:$A$1000</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>